--- a/Argumental/argumental-app/public/argumental-financial-model.xlsx
+++ b/Argumental/argumental-app/public/argumental-financial-model.xlsx
@@ -20,12 +20,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;0.00"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0)"/>
+    <numFmt numFmtId="168" formatCode="#,##0&quot;x&quot;"/>
+    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0)"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -101,12 +102,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EB2C35"/>
+        <fgColor rgb="001165C6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001165C6"/>
+        <fgColor rgb="00EB2C35"/>
       </patternFill>
     </fill>
   </fills>
@@ -136,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -172,6 +173,9 @@
     <xf numFmtId="167" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -191,13 +195,16 @@
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -563,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -729,101 +736,191 @@
       <c r="A25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>What this model is honest about</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Year 1 stated goal</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Voting revenue is gated by viewer reach, not by price.  ARPU is fixed at</t>
+          <t xml:space="preserve">  · 100,000 live viewers per bout by end of Year 1.  The Y1 average of</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    $5 per vote with a $10/week cap — voters CAN vote multiple bouts per week</t>
+          <t xml:space="preserve">    30,000 reflects a back-weighted ramp toward that target — the league</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    but the model conservatively assumes one vote per viewer per bout.</t>
+          <t xml:space="preserve">    starts smaller, compounds weekly through paid search and creator pull.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · Sponsor revenue ramps in Year 2.  Year 1 carries no sponsor income —</t>
-        </is>
-      </c>
+      <c r="A30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    the format proves itself first, then sells against verified audience data.</t>
+          <t>Reach assumption — the 41× multiplier</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Mux delivery cost scales with viewers; included as a real per-bout COGS.</t>
+          <t xml:space="preserve">  · Live + post-live replay = 41× total impressions per bout.  Each</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Charity payout is 18% of gross voting revenue, accounted as COGS so it</t>
+          <t xml:space="preserve">    archived bout earns ~40× the live-viewer count over its first 24 hours</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    flows through gross margin (matches the donor-receipt model).</t>
+          <t xml:space="preserve">    via clips, embeds, and on-demand replay.  Replay viewers don't vote</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr"/>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (the bout is over) but they DO drive Mux delivery cost and sponsor</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>What this model deliberately omits</t>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    package value.  The model accounts for both.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · IP / licensing revenue (international territories, format licensing).</t>
-        </is>
-      </c>
+      <c r="A37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Treated as upside, not assumed.</t>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>What this model is honest about</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Working-capital and payment-processor float.</t>
+          <t xml:space="preserve">  · Voting revenue is gated by live viewer reach, not by price.  ARPU is</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    fixed at $5 per vote with a $10/week cap — voters CAN vote multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    bouts per week but the model conservatively assumes one vote per</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    live viewer per bout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Sponsor revenue ramps in Year 2.  Year 1 carries no sponsor income —</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    the format proves itself first, then sells against verified audience data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Mux delivery cost scales with viewers (live + replay); included as a</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    real per-bout COGS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Charity payout is 18% of gross voting revenue, accounted as COGS so it</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    flows through gross margin (matches the donor-receipt model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>What this model deliberately omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · IP / licensing revenue (international territories, format licensing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Treated as upside, not assumed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Working-capital and payment-processor float.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Tax — model is pre-tax EBITDA only.</t>
         </is>
@@ -840,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -926,21 +1023,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Avg concurrent viewers / bout</t>
+          <t>Avg concurrent live viewers / bout</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>12000</v>
+        <v>30000</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>140000</v>
+        <v>250000</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Live + 24h replay</t>
+          <t>Y1 ramp targets 100K EOY</t>
         </is>
       </c>
     </row>
@@ -1007,14 +1104,14 @@
         <v>0</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>60000</v>
+        <v>75000</v>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Title slot</t>
+          <t>Title slot · 41× reach</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1434,7 @@
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>AUDIENCE BEHAVIOR</t>
         </is>
       </c>
       <c r="B33" s="6" t="n"/>
@@ -1348,7 +1445,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Avg minutes watched / viewer / bout</t>
+          <t>Avg minutes watched / live viewer</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
@@ -1362,7 +1459,49 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Drives Mux delivery cost</t>
+          <t>Drives live Mux delivery cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Post-live replay multiplier</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="C35" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>Replay views = live × this. Bout 24h+ archive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Avg minutes watched / replay viewer</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>Highlights &amp; clips, not full bout</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1407,22 +1546,22 @@
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>3-Yr Total</t>
         </is>
@@ -1434,19 +1573,19 @@
           <t>Bouts per year</t>
         </is>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="17">
         <f>Assumptions!B7</f>
         <v/>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="17">
         <f>Assumptions!C7</f>
         <v/>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="17">
         <f>Assumptions!D7</f>
         <v/>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="18">
         <f>SUM(B6:D6)</f>
         <v/>
       </c>
@@ -1457,15 +1596,15 @@
           <t>Avg concurrent viewers / bout</t>
         </is>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="17">
         <f>Assumptions!B8</f>
         <v/>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="17">
         <f>Assumptions!C8</f>
         <v/>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="17">
         <f>Assumptions!D8</f>
         <v/>
       </c>
@@ -1476,19 +1615,19 @@
           <t>Annual viewer-bouts</t>
         </is>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="17">
         <f>B6*B7</f>
         <v/>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="17">
         <f>C6*C7</f>
         <v/>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="17">
         <f>D6*D7</f>
         <v/>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="18">
         <f>SUM(B8:D8)</f>
         <v/>
       </c>
@@ -1499,15 +1638,15 @@
           <t>Voter conversion rate</t>
         </is>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="19">
         <f>Assumptions!B9</f>
         <v/>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>Assumptions!C9</f>
         <v/>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="19">
         <f>Assumptions!D9</f>
         <v/>
       </c>
@@ -1518,15 +1657,15 @@
           <t>Votes per bout</t>
         </is>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="17">
         <f>B7*B9</f>
         <v/>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="17">
         <f>C7*C9</f>
         <v/>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="17">
         <f>D7*D9</f>
         <v/>
       </c>
@@ -1537,19 +1676,19 @@
           <t>Annual votes</t>
         </is>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="18">
         <f>B6*B10</f>
         <v/>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="18">
         <f>C6*C10</f>
         <v/>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="18">
         <f>D6*D10</f>
         <v/>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="18">
         <f>SUM(B11:D11)</f>
         <v/>
       </c>
@@ -1557,18 +1696,18 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Avg minutes watched / viewer</t>
-        </is>
-      </c>
-      <c r="B13" s="16">
+          <t>Avg minutes watched / live viewer</t>
+        </is>
+      </c>
+      <c r="B13" s="17">
         <f>Assumptions!B34</f>
         <v/>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="17">
         <f>Assumptions!C34</f>
         <v/>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="17">
         <f>Assumptions!D34</f>
         <v/>
       </c>
@@ -1579,20 +1718,111 @@
           <t>Annual viewer-hours delivered (Mux)</t>
         </is>
       </c>
-      <c r="B14" s="17">
-        <f>B8*B13/60</f>
-        <v/>
-      </c>
-      <c r="C14" s="17">
-        <f>C8*C13/60</f>
-        <v/>
-      </c>
-      <c r="D14" s="17">
-        <f>D8*D13/60</f>
-        <v/>
-      </c>
-      <c r="E14" s="17">
+      <c r="B14" s="18">
+        <f>B8*(B13+Assumptions!B35*Assumptions!B36)/60</f>
+        <v/>
+      </c>
+      <c r="C14" s="18">
+        <f>C8*(C13+Assumptions!C35*Assumptions!C36)/60</f>
+        <v/>
+      </c>
+      <c r="D14" s="18">
+        <f>D8*(D13+Assumptions!D35*Assumptions!D36)/60</f>
+        <v/>
+      </c>
+      <c r="E14" s="18">
         <f>SUM(B14:D14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>REACH BEYOND LIVE</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="n"/>
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="21" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Post-live replay multiplier</t>
+        </is>
+      </c>
+      <c r="B17" s="22">
+        <f>Assumptions!B35</f>
+        <v/>
+      </c>
+      <c r="C17" s="22">
+        <f>Assumptions!C35</f>
+        <v/>
+      </c>
+      <c r="D17" s="22">
+        <f>Assumptions!D35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Replay viewers / bout</t>
+        </is>
+      </c>
+      <c r="B18" s="17">
+        <f>B7*B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="17">
+        <f>C7*C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="17">
+        <f>D7*D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Total reach / bout (live + replay)</t>
+        </is>
+      </c>
+      <c r="B19" s="17">
+        <f>B7+B18</f>
+        <v/>
+      </c>
+      <c r="C19" s="17">
+        <f>C7+C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="17">
+        <f>D7+D18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Annual total impressions</t>
+        </is>
+      </c>
+      <c r="B20" s="18">
+        <f>B6*B19</f>
+        <v/>
+      </c>
+      <c r="C20" s="18">
+        <f>C6*C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="18">
+        <f>D6*D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="18">
+        <f>SUM(B20:D20)</f>
         <v/>
       </c>
     </row>
@@ -1633,37 +1863,37 @@
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="5" t="inlineStr"/>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>3-Yr Total</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>REVENUE</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n"/>
-      <c r="C6" s="20" t="n"/>
-      <c r="D6" s="20" t="n"/>
-      <c r="E6" s="20" t="n"/>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
+      <c r="E6" s="24" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1671,19 +1901,19 @@
           <t>Voting revenue</t>
         </is>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="25">
         <f>'Bouts &amp; Audience'!B11*Assumptions!B10</f>
         <v/>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="25">
         <f>'Bouts &amp; Audience'!C11*Assumptions!C10</f>
         <v/>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="25">
         <f>'Bouts &amp; Audience'!D11*Assumptions!D10</f>
         <v/>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="25">
         <f>SUM(B7:D7)</f>
         <v/>
       </c>
@@ -1694,19 +1924,19 @@
           <t>Sponsor revenue</t>
         </is>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="25">
         <f>Assumptions!B7*Assumptions!B14*Assumptions!B13</f>
         <v/>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="25">
         <f>Assumptions!C7*Assumptions!C14*Assumptions!C13</f>
         <v/>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="25">
         <f>Assumptions!D7*Assumptions!D14*Assumptions!D13</f>
         <v/>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="25">
         <f>SUM(B8:D8)</f>
         <v/>
       </c>
@@ -1717,33 +1947,33 @@
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="26">
         <f>SUM(B7:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="26">
         <f>SUM(C7:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="26">
         <f>SUM(D7:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="26">
         <f>SUM(B9:D9)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>VARIABLE COSTS  ·  COGS</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="24" t="n"/>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1751,15 +1981,15 @@
           <t>Mux delivery (CDN)</t>
         </is>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="25">
         <f>'Bouts &amp; Audience'!B14*Assumptions!B17</f>
         <v/>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="25">
         <f>'Bouts &amp; Audience'!C14*Assumptions!C17</f>
         <v/>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="25">
         <f>'Bouts &amp; Audience'!D14*Assumptions!D17</f>
         <v/>
       </c>
@@ -1770,15 +2000,15 @@
           <t>Mux ingest</t>
         </is>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="25">
         <f>Assumptions!B7*Assumptions!B18</f>
         <v/>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="25">
         <f>Assumptions!C7*Assumptions!C18</f>
         <v/>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="25">
         <f>Assumptions!D7*Assumptions!D18</f>
         <v/>
       </c>
@@ -1789,15 +2019,15 @@
           <t>Stripe processing</t>
         </is>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="25">
         <f>B7*Assumptions!B19+'Bouts &amp; Audience'!B11*Assumptions!B20</f>
         <v/>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="25">
         <f>C7*Assumptions!C19+'Bouts &amp; Audience'!C11*Assumptions!C20</f>
         <v/>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="25">
         <f>D7*Assumptions!D19+'Bouts &amp; Audience'!D11*Assumptions!D20</f>
         <v/>
       </c>
@@ -1808,15 +2038,15 @@
           <t>Charity payout (18% of vote rev)</t>
         </is>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="25">
         <f>B7*Assumptions!B21</f>
         <v/>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="25">
         <f>C7*Assumptions!C21</f>
         <v/>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="25">
         <f>D7*Assumptions!D21</f>
         <v/>
       </c>
@@ -1827,15 +2057,15 @@
           <t>Debater honorariums</t>
         </is>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="25">
         <f>Assumptions!B7*Assumptions!B22</f>
         <v/>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="25">
         <f>Assumptions!C7*Assumptions!C22</f>
         <v/>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="25">
         <f>Assumptions!D7*Assumptions!D22</f>
         <v/>
       </c>
@@ -1846,15 +2076,15 @@
           <t>Production</t>
         </is>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="25">
         <f>Assumptions!B7*Assumptions!B23</f>
         <v/>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="25">
         <f>Assumptions!C7*Assumptions!C23</f>
         <v/>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="25">
         <f>Assumptions!D7*Assumptions!D23</f>
         <v/>
       </c>
@@ -1865,19 +2095,19 @@
           <t>Total variable cost</t>
         </is>
       </c>
-      <c r="B18" s="22">
+      <c r="B18" s="26">
         <f>SUM(B12:B17)</f>
         <v/>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="26">
         <f>SUM(C12:C17)</f>
         <v/>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="26">
         <f>SUM(D12:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="26">
         <f>SUM(B18:D18)</f>
         <v/>
       </c>
@@ -1899,19 +2129,19 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B21" s="22">
+      <c r="B21" s="26">
         <f>B9-B18</f>
         <v/>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="26">
         <f>C9-C18</f>
         <v/>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="26">
         <f>D9-D18</f>
         <v/>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="26">
         <f>SUM(B21:D21)</f>
         <v/>
       </c>
@@ -1922,29 +2152,29 @@
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B22" s="18">
+      <c r="B22" s="19">
         <f>IFERROR(B21/B9,0)</f>
         <v/>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="19">
         <f>IFERROR(C21/C9,0)</f>
         <v/>
       </c>
-      <c r="D22" s="18">
+      <c r="D22" s="19">
         <f>IFERROR(D21/D9,0)</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>FIXED OPEX</t>
         </is>
       </c>
-      <c r="B24" s="24" t="n"/>
-      <c r="C24" s="24" t="n"/>
-      <c r="D24" s="24" t="n"/>
-      <c r="E24" s="24" t="n"/>
+      <c r="B24" s="21" t="n"/>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -1952,15 +2182,15 @@
           <t>Headcount cost</t>
         </is>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="25">
         <f>Assumptions!B26*Assumptions!B27</f>
         <v/>
       </c>
-      <c r="C25" s="21">
+      <c r="C25" s="25">
         <f>Assumptions!C26*Assumptions!C27</f>
         <v/>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="25">
         <f>Assumptions!D26*Assumptions!D27</f>
         <v/>
       </c>
@@ -1971,15 +2201,15 @@
           <t>Paid search &amp; acquisition</t>
         </is>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="25">
         <f>Assumptions!B28</f>
         <v/>
       </c>
-      <c r="C26" s="21">
+      <c r="C26" s="25">
         <f>Assumptions!C28</f>
         <v/>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="25">
         <f>Assumptions!D28</f>
         <v/>
       </c>
@@ -1990,15 +2220,15 @@
           <t>Brand &amp; creator marketing</t>
         </is>
       </c>
-      <c r="B27" s="21">
+      <c r="B27" s="25">
         <f>Assumptions!B29</f>
         <v/>
       </c>
-      <c r="C27" s="21">
+      <c r="C27" s="25">
         <f>Assumptions!C29</f>
         <v/>
       </c>
-      <c r="D27" s="21">
+      <c r="D27" s="25">
         <f>Assumptions!D29</f>
         <v/>
       </c>
@@ -2009,15 +2239,15 @@
           <t>G&amp;A, tooling, infra</t>
         </is>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="25">
         <f>Assumptions!B30</f>
         <v/>
       </c>
-      <c r="C28" s="21">
+      <c r="C28" s="25">
         <f>Assumptions!C30</f>
         <v/>
       </c>
-      <c r="D28" s="21">
+      <c r="D28" s="25">
         <f>Assumptions!D30</f>
         <v/>
       </c>
@@ -2028,15 +2258,15 @@
           <t>Legal, accounting, insurance</t>
         </is>
       </c>
-      <c r="B29" s="21">
+      <c r="B29" s="25">
         <f>Assumptions!B31</f>
         <v/>
       </c>
-      <c r="C29" s="21">
+      <c r="C29" s="25">
         <f>Assumptions!C31</f>
         <v/>
       </c>
-      <c r="D29" s="21">
+      <c r="D29" s="25">
         <f>Assumptions!D31</f>
         <v/>
       </c>
@@ -2047,19 +2277,19 @@
           <t>Total fixed opex</t>
         </is>
       </c>
-      <c r="B30" s="22">
+      <c r="B30" s="26">
         <f>SUM(B25:B29)</f>
         <v/>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="26">
         <f>SUM(C25:C29)</f>
         <v/>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="26">
         <f>SUM(D25:D29)</f>
         <v/>
       </c>
-      <c r="E30" s="22">
+      <c r="E30" s="26">
         <f>SUM(B30:D30)</f>
         <v/>
       </c>
@@ -2081,19 +2311,19 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B33" s="22">
+      <c r="B33" s="26">
         <f>B21-B30</f>
         <v/>
       </c>
-      <c r="C33" s="22">
+      <c r="C33" s="26">
         <f>C21-C30</f>
         <v/>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="26">
         <f>D21-D30</f>
         <v/>
       </c>
-      <c r="E33" s="22">
+      <c r="E33" s="26">
         <f>SUM(B33:D33)</f>
         <v/>
       </c>
@@ -2104,15 +2334,15 @@
           <t>EBITDA margin %</t>
         </is>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="19">
         <f>IFERROR(B33/B9,0)</f>
         <v/>
       </c>
-      <c r="C34" s="18">
+      <c r="C34" s="19">
         <f>IFERROR(C33/C9,0)</f>
         <v/>
       </c>
-      <c r="D34" s="18">
+      <c r="D34" s="19">
         <f>IFERROR(D33/D9,0)</f>
         <v/>
       </c>
@@ -2161,17 +2391,17 @@
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="5" t="inlineStr"/>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Year 1 scale</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>Year 2 scale</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Year 3 scale</t>
         </is>
@@ -2183,15 +2413,15 @@
           <t>Avg viewers / bout</t>
         </is>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="17">
         <f>Assumptions!B8</f>
         <v/>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="17">
         <f>Assumptions!C8</f>
         <v/>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="17">
         <f>Assumptions!D8</f>
         <v/>
       </c>
@@ -2202,28 +2432,28 @@
           <t>Voters / bout</t>
         </is>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="17">
         <f>B6*Assumptions!B9</f>
         <v/>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="17">
         <f>C6*Assumptions!C9</f>
         <v/>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="17">
         <f>D6*Assumptions!D9</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>REVENUE / BOUT</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n"/>
-      <c r="C9" s="20" t="n"/>
-      <c r="D9" s="20" t="n"/>
+      <c r="B9" s="24" t="n"/>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -2231,15 +2461,15 @@
           <t>Voting</t>
         </is>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="25">
         <f>B7*Assumptions!B10</f>
         <v/>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="25">
         <f>C7*Assumptions!C10</f>
         <v/>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="25">
         <f>D7*Assumptions!D10</f>
         <v/>
       </c>
@@ -2250,15 +2480,15 @@
           <t>Sponsor share</t>
         </is>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="25">
         <f>Assumptions!B13*Assumptions!B14</f>
         <v/>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="25">
         <f>Assumptions!C13*Assumptions!C14</f>
         <v/>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="25">
         <f>Assumptions!D13*Assumptions!D14</f>
         <v/>
       </c>
@@ -2269,45 +2499,45 @@
           <t>Total revenue / bout</t>
         </is>
       </c>
-      <c r="B12" s="22">
+      <c r="B12" s="26">
         <f>SUM(B10:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="26">
         <f>SUM(C10:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="26">
         <f>SUM(D10:D11)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>VARIABLE COST / BOUT</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n"/>
-      <c r="C14" s="24" t="n"/>
-      <c r="D14" s="24" t="n"/>
+      <c r="B14" s="21" t="n"/>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="21" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Mux delivery</t>
-        </is>
-      </c>
-      <c r="B15" s="21">
-        <f>B6*Assumptions!B34/60*Assumptions!B17</f>
-        <v/>
-      </c>
-      <c r="C15" s="21">
-        <f>C6*Assumptions!C34/60*Assumptions!C17</f>
-        <v/>
-      </c>
-      <c r="D15" s="21">
-        <f>D6*Assumptions!D34/60*Assumptions!D17</f>
+          <t>Mux delivery (live + replay)</t>
+        </is>
+      </c>
+      <c r="B15" s="25">
+        <f>B6*(Assumptions!B34+Assumptions!B35*Assumptions!B36)/60*Assumptions!B17</f>
+        <v/>
+      </c>
+      <c r="C15" s="25">
+        <f>C6*(Assumptions!C34+Assumptions!C35*Assumptions!C36)/60*Assumptions!C17</f>
+        <v/>
+      </c>
+      <c r="D15" s="25">
+        <f>D6*(Assumptions!D34+Assumptions!D35*Assumptions!D36)/60*Assumptions!D17</f>
         <v/>
       </c>
     </row>
@@ -2317,15 +2547,15 @@
           <t>Mux ingest</t>
         </is>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="25">
         <f>Assumptions!B18</f>
         <v/>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="25">
         <f>Assumptions!C18</f>
         <v/>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="25">
         <f>Assumptions!D18</f>
         <v/>
       </c>
@@ -2336,15 +2566,15 @@
           <t>Stripe processing</t>
         </is>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="25">
         <f>B10*Assumptions!B19+B7*Assumptions!B20</f>
         <v/>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="25">
         <f>C10*Assumptions!C19+C7*Assumptions!C20</f>
         <v/>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="25">
         <f>D10*Assumptions!D19+D7*Assumptions!D20</f>
         <v/>
       </c>
@@ -2355,15 +2585,15 @@
           <t>Charity payout</t>
         </is>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="25">
         <f>B10*Assumptions!B21</f>
         <v/>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="25">
         <f>C10*Assumptions!C21</f>
         <v/>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="25">
         <f>D10*Assumptions!D21</f>
         <v/>
       </c>
@@ -2374,15 +2604,15 @@
           <t>Debater honorariums</t>
         </is>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="25">
         <f>Assumptions!B22</f>
         <v/>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="25">
         <f>Assumptions!C22</f>
         <v/>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="25">
         <f>Assumptions!D22</f>
         <v/>
       </c>
@@ -2393,15 +2623,15 @@
           <t>Production</t>
         </is>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="25">
         <f>Assumptions!B23</f>
         <v/>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="25">
         <f>Assumptions!C23</f>
         <v/>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="25">
         <f>Assumptions!D23</f>
         <v/>
       </c>
@@ -2412,15 +2642,15 @@
           <t>Total variable cost / bout</t>
         </is>
       </c>
-      <c r="B21" s="22">
+      <c r="B21" s="26">
         <f>SUM(B15:B20)</f>
         <v/>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="26">
         <f>SUM(C15:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="26">
         <f>SUM(D15:D20)</f>
         <v/>
       </c>
@@ -2441,15 +2671,15 @@
           <t>Contribution $</t>
         </is>
       </c>
-      <c r="B24" s="22">
+      <c r="B24" s="26">
         <f>B12-B21</f>
         <v/>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="26">
         <f>C12-C21</f>
         <v/>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="26">
         <f>D12-D21</f>
         <v/>
       </c>
@@ -2460,15 +2690,15 @@
           <t>Contribution %</t>
         </is>
       </c>
-      <c r="B25" s="18">
+      <c r="B25" s="19">
         <f>IFERROR(B24/B12,0)</f>
         <v/>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="19">
         <f>IFERROR(C24/C12,0)</f>
         <v/>
       </c>
-      <c r="D25" s="18">
+      <c r="D25" s="19">
         <f>IFERROR(D24/D12,0)</f>
         <v/>
       </c>

--- a/Argumental/argumental-app/public/argumental-financial-model.xlsx
+++ b/Argumental/argumental-app/public/argumental-financial-model.xlsx
@@ -1259,17 +1259,17 @@
         </is>
       </c>
       <c r="B22" s="11" t="n">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>80000</v>
+        <v>25000</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>120000</v>
+        <v>25000</v>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Both debaters</t>
+          <t>Capped at $25K (both)</t>
         </is>
       </c>
     </row>

--- a/Argumental/argumental-app/public/argumental-financial-model.xlsx
+++ b/Argumental/argumental-app/public/argumental-financial-model.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -603,80 +603,80 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>All five tabs are linked: change a cell on Assumptions and every downstream</t>
+          <t>Inputs are loaded from src/lib/financialModelInputs.json — the same file that</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>number updates.</t>
+          <t>drives /deck and /model on the website. Edit the JSON, re-run the build</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>script, and all three views stay in lockstep.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Tabs</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. Read Me — this page.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Assumptions — every input the model uses, in one place. Cells with a</t>
+          <t xml:space="preserve">  1. Read Me — this page.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     pale-blue fill are inputs you can edit; everything else is a formula.</t>
+          <t xml:space="preserve">  2. Assumptions — every input the model uses, in one place. Cells with a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Bouts &amp; Audience — month-by-month viewer ramp and bouts per year.</t>
+          <t xml:space="preserve">     pale-blue fill are inputs; everything else is a formula.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. P&amp;L (3-Year) — revenue, variable costs, gross margin, fixed opex,</t>
+          <t xml:space="preserve">  3. Bouts &amp; Audience — viewer ramp, replay reach, votes per year.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     EBITDA. Year-over-year columns plus a running 3-year total.</t>
+          <t xml:space="preserve">  4. P&amp;L (3-Year) — revenue, variable costs, gross margin, fixed opex,</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. Unit Economics — contribution margin per bout at three audience scales,</t>
+          <t xml:space="preserve">     EBITDA. Year-over-year columns plus a running 3-year total.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     so you can read the operating leverage at a glance.</t>
+          <t xml:space="preserve">  5. Unit Economics — contribution margin per bout at three audience scales.</t>
         </is>
       </c>
     </row>
@@ -707,220 +707,171 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Bouts cadence is one per Sunday — 4 / month, 48 / year. Each bout is a</t>
+          <t xml:space="preserve">  · Bouts cadence is one per Sunday — 4 / month, 48 / year.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    24-minute, two-stream live event archived for on-demand replay.</t>
+          <t xml:space="preserve">  · All dollar figures are in USD.  Years labeled 2026 / 2027 / 2028.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · All dollar figures are in USD.  Years labeled 2026 / 2027 / 2028 to match</t>
-        </is>
-      </c>
+      <c r="A23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    the deck timeline.</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 stated goal</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr"/>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 100,000 live viewers per bout by end of Year 1. The Y1 average of</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Year 1 stated goal</t>
+          <t xml:space="preserve">    30,000 reflects a back-weighted ramp toward that target.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · 100,000 live viewers per bout by end of Year 1.  The Y1 average of</t>
-        </is>
-      </c>
+      <c r="A27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    30,000 reflects a back-weighted ramp toward that target — the league</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Reach assumption — the 41× multiplier</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    starts smaller, compounds weekly through paid search and creator pull.</t>
+          <t xml:space="preserve">  · Live + post-live replay = 41× total impressions per bout. Each</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr"/>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    archived bout earns ~40× the live-viewer count over its first 24 hours</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Reach assumption — the 41× multiplier</t>
+          <t xml:space="preserve">    via clips, embeds, and on-demand replay. Replay viewers don't vote</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Live + post-live replay = 41× total impressions per bout.  Each</t>
+          <t xml:space="preserve">    (the bout is over) but they DO drive Mux delivery cost and sponsor</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    archived bout earns ~40× the live-viewer count over its first 24 hours</t>
+          <t xml:space="preserve">    package value.  The model accounts for both.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    via clips, embeds, and on-demand replay.  Replay viewers don't vote</t>
-        </is>
-      </c>
+      <c r="A34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    (the bout is over) but they DO drive Mux delivery cost and sponsor</t>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>What this model is honest about</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    package value.  The model accounts for both.</t>
+          <t xml:space="preserve">  · Voting revenue is gated by live viewer reach, not by price.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr"/>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Sponsor revenue ramps in Year 2.  Year 1 carries no sponsor income.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>What this model is honest about</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Mux delivery cost scales with viewers (live + replay); included as a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Voting revenue is gated by live viewer reach, not by price.  ARPU is</t>
+          <t xml:space="preserve">    real per-bout COGS.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    fixed at $5 per vote with a $10/week cap — voters CAN vote multiple</t>
+          <t xml:space="preserve">  · Charity payout is 18% of gross voting revenue, accounted as COGS.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    bouts per week but the model conservatively assumes one vote per</t>
+          <t xml:space="preserve">  · Debater honorariums capped at $25K / bout (covers both debaters).</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    live viewer per bout.</t>
-        </is>
-      </c>
+      <c r="A42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · Sponsor revenue ramps in Year 2.  Year 1 carries no sponsor income —</t>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>What this model deliberately omits</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    the format proves itself first, then sells against verified audience data.</t>
+          <t xml:space="preserve">  · IP / licensing revenue (international territories, format licensing).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Mux delivery cost scales with viewers (live + replay); included as a</t>
+          <t xml:space="preserve">    Treated as upside, not assumed.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    real per-bout COGS.</t>
+          <t xml:space="preserve">  · Working-capital and payment-processor float.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · Charity payout is 18% of gross voting revenue, accounted as COGS so it</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    flows through gross margin (matches the donor-receipt model).</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>What this model deliberately omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · IP / licensing revenue (international territories, format licensing).</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Treated as upside, not assumed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · Working-capital and payment-processor float.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Tax — model is pre-tax EBITDA only.</t>
         </is>
@@ -1480,7 +1431,7 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Replay views = live × this. Bout 24h+ archive.</t>
+          <t>Replay views = live × this</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1452,7 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Highlights &amp; clips, not full bout</t>
+          <t>Highlights &amp; clips</t>
         </is>
       </c>
     </row>

--- a/Argumental/argumental-app/public/argumental-financial-model.xlsx
+++ b/Argumental/argumental-app/public/argumental-financial-model.xlsx
@@ -164,13 +164,13 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="168" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -807,71 +807,85 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Sponsor revenue ramps in Year 2.  Year 1 carries no sponsor income.</t>
+          <t xml:space="preserve">  · Mux delivery cost scales with viewers (live + replay); included as a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Mux delivery cost scales with viewers (live + replay); included as a</t>
+          <t xml:space="preserve">    real per-bout COGS.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    real per-bout COGS.</t>
+          <t xml:space="preserve">  · Charity payout is 18% of gross voting revenue, accounted as COGS.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Charity payout is 18% of gross voting revenue, accounted as COGS.</t>
+          <t xml:space="preserve">  · Debater honorariums capped at $25K / bout (covers both debaters).</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · Debater honorariums capped at $25K / bout (covers both debaters).</t>
-        </is>
-      </c>
+      <c r="A41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr"/>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>What this model deliberately omits</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>What this model deliberately omits</t>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Sponsorship revenue. Title slots, category exclusives, and brand</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · IP / licensing revenue (international territories, format licensing).</t>
+          <t xml:space="preserve">    integrations are real revenue lines for the league but treated as</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Treated as upside, not assumed.</t>
+          <t xml:space="preserve">    upside here — the conservative case is voting revenue only.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Working-capital and payment-processor float.</t>
+          <t xml:space="preserve">  · IP / licensing revenue (international territories, format licensing).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · On-demand archive monetization, white-label league, ticketing, merch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Working-capital and payment-processor float.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Tax — model is pre-tax EBITDA only.</t>
         </is>
@@ -1034,59 +1048,6 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>SPONSORSHIP</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Sponsor revenue / bout (USD)</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>Title slot · 41× reach</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Sponsored bouts (% of cadence)</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>Brand fit</t>
-        </is>
-      </c>
-    </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -1104,13 +1065,13 @@
           <t>Mux delivery $/viewer-hour</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="12" t="n">
         <v>0.06</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="12" t="n">
         <v>0.06</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="12" t="n">
         <v>0.05</v>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -1167,13 +1128,13 @@
           <t>Stripe per-vote fee</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
+      <c r="B20" s="13" t="n">
         <v>0.3</v>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C20" s="13" t="n">
         <v>0.3</v>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="13" t="n">
         <v>0.3</v>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -1188,13 +1149,13 @@
           <t>Charity payout (% of vote rev)</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="14" t="n">
         <v>0.18</v>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="14" t="n">
         <v>0.18</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D21" s="14" t="n">
         <v>0.18</v>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1869,29 +1830,6 @@
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Sponsor revenue</t>
-        </is>
-      </c>
-      <c r="B8" s="25">
-        <f>Assumptions!B7*Assumptions!B14*Assumptions!B13</f>
-        <v/>
-      </c>
-      <c r="C8" s="25">
-        <f>Assumptions!C7*Assumptions!C14*Assumptions!C13</f>
-        <v/>
-      </c>
-      <c r="D8" s="25">
-        <f>Assumptions!D7*Assumptions!D14*Assumptions!D13</f>
-        <v/>
-      </c>
-      <c r="E8" s="25">
-        <f>SUM(B8:D8)</f>
-        <v/>
-      </c>
-    </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
@@ -1899,15 +1837,15 @@
         </is>
       </c>
       <c r="B9" s="26">
-        <f>SUM(B7:B8)</f>
+        <f>B7</f>
         <v/>
       </c>
       <c r="C9" s="26">
-        <f>SUM(C7:C8)</f>
+        <f>C7</f>
         <v/>
       </c>
       <c r="D9" s="26">
-        <f>SUM(D7:D8)</f>
+        <f>D7</f>
         <v/>
       </c>
       <c r="E9" s="26">
@@ -2425,25 +2363,6 @@
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Sponsor share</t>
-        </is>
-      </c>
-      <c r="B11" s="25">
-        <f>Assumptions!B13*Assumptions!B14</f>
-        <v/>
-      </c>
-      <c r="C11" s="25">
-        <f>Assumptions!C13*Assumptions!C14</f>
-        <v/>
-      </c>
-      <c r="D11" s="25">
-        <f>Assumptions!D13*Assumptions!D14</f>
-        <v/>
-      </c>
-    </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -2451,15 +2370,15 @@
         </is>
       </c>
       <c r="B12" s="26">
-        <f>SUM(B10:B11)</f>
+        <f>B10</f>
         <v/>
       </c>
       <c r="C12" s="26">
-        <f>SUM(C10:C11)</f>
+        <f>C10</f>
         <v/>
       </c>
       <c r="D12" s="26">
-        <f>SUM(D10:D11)</f>
+        <f>D10</f>
         <v/>
       </c>
     </row>

--- a/Argumental/argumental-app/public/argumental-financial-model.xlsx
+++ b/Argumental/argumental-app/public/argumental-financial-model.xlsx
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -171,6 +171,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="168" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -570,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -731,161 +734,168 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · 100,000 live viewers per bout by end of Year 1. The Y1 average of</t>
+          <t xml:space="preserve">  · 60,000 live viewers per bout by end of Year 1.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    30,000 reflects a back-weighted ramp toward that target.</t>
-        </is>
-      </c>
+      <c r="A26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr"/>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Reach assumption — the 41× multiplier</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Reach assumption — the 41× multiplier</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Live + post-live replay = 41× total impressions per bout. Each</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Live + post-live replay = 41× total impressions per bout. Each</t>
+          <t xml:space="preserve">    archived bout earns ~40× the live-viewer count over its first 24 hours</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    archived bout earns ~40× the live-viewer count over its first 24 hours</t>
+          <t xml:space="preserve">    via clips, embeds, and on-demand replay. Replay viewers don't vote</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    via clips, embeds, and on-demand replay. Replay viewers don't vote</t>
+          <t xml:space="preserve">    (the bout is over) but they DO drive Mux delivery cost and sponsor</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (the bout is over) but they DO drive Mux delivery cost and sponsor</t>
+          <t xml:space="preserve">    package value.  The model accounts for both.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    package value.  The model accounts for both.</t>
-        </is>
-      </c>
+      <c r="A33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr"/>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>What this model is honest about</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>What this model is honest about</t>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Voting revenue is gated by live viewer reach, not by price.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Voting revenue is gated by live viewer reach, not by price.</t>
+          <t xml:space="preserve">  · Mux delivery cost scales with viewers (live + replay); included as a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Mux delivery cost scales with viewers (live + replay); included as a</t>
+          <t xml:space="preserve">    real per-bout COGS.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    real per-bout COGS.</t>
+          <t xml:space="preserve">  · Charity payout is 18% of gross voting revenue, accounted as COGS.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Charity payout is 18% of gross voting revenue, accounted as COGS.</t>
+          <t xml:space="preserve">  · Debater honorariums: Y1 flat $10K / bout (cash to attract talent),</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Debater honorariums capped at $25K / bout (covers both debaters).</t>
+          <t xml:space="preserve">    Y2/Y3 revenue share — 5% / 3% of per-bout voting purse — to align</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr"/>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    debater incentives with audience growth as the league matures.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>What this model deliberately omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · Sponsorship revenue. Title slots, category exclusives, and brand</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    integrations are real revenue lines for the league but treated as</t>
+          <t xml:space="preserve">  · Sponsorship revenue. Title slots, category exclusives, and brand</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    upside here — the conservative case is voting revenue only.</t>
+          <t xml:space="preserve">    integrations are real revenue lines for the league but treated as</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · IP / licensing revenue (international territories, format licensing).</t>
+          <t xml:space="preserve">    upside here — the conservative case is voting revenue only.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · On-demand archive monetization, white-label league, ticketing, merch.</t>
+          <t xml:space="preserve">  · IP / licensing revenue (international territories, format licensing).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Working-capital and payment-processor float.</t>
+          <t xml:space="preserve">  · On-demand archive monetization, white-label league, ticketing, merch.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Working-capital and payment-processor float.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  · Tax — model is pre-tax EBITDA only.</t>
         </is>
@@ -992,13 +1002,13 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>30000</v>
+        <v>60000</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>100000</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>250000</v>
+        <v>125000</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
@@ -1171,17 +1181,19 @@
         </is>
       </c>
       <c r="B22" s="11" t="n">
-        <v>25000</v>
-      </c>
-      <c r="C22" s="11" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>25000</v>
+        <v>10000</v>
+      </c>
+      <c r="C22" s="15">
+        <f>C8*C9*C10*0.05</f>
+        <v/>
+      </c>
+      <c r="D22" s="15">
+        <f>D8*D9*D10*0.03</f>
+        <v/>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Capped at $25K (both)</t>
+          <t>Y1 flat $10,000 · Y2 5% of purse · Y3 3% of purse</t>
         </is>
       </c>
     </row>
@@ -1192,13 +1204,13 @@
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>18000</v>
+        <v>10000</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
@@ -1381,13 +1393,13 @@
           <t>Post-live replay multiplier</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
+      <c r="B35" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="C35" s="15" t="n">
+      <c r="C35" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="D35" s="15" t="n">
+      <c r="D35" s="16" t="n">
         <v>40</v>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -1458,22 +1470,22 @@
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>3-Yr Total</t>
         </is>
@@ -1485,19 +1497,19 @@
           <t>Bouts per year</t>
         </is>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="18">
         <f>Assumptions!B7</f>
         <v/>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="18">
         <f>Assumptions!C7</f>
         <v/>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="18">
         <f>Assumptions!D7</f>
         <v/>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <f>SUM(B6:D6)</f>
         <v/>
       </c>
@@ -1508,15 +1520,15 @@
           <t>Avg concurrent viewers / bout</t>
         </is>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="18">
         <f>Assumptions!B8</f>
         <v/>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="18">
         <f>Assumptions!C8</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="18">
         <f>Assumptions!D8</f>
         <v/>
       </c>
@@ -1527,19 +1539,19 @@
           <t>Annual viewer-bouts</t>
         </is>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="18">
         <f>B6*B7</f>
         <v/>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="18">
         <f>C6*C7</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="18">
         <f>D6*D7</f>
         <v/>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="19">
         <f>SUM(B8:D8)</f>
         <v/>
       </c>
@@ -1550,15 +1562,15 @@
           <t>Voter conversion rate</t>
         </is>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="20">
         <f>Assumptions!B9</f>
         <v/>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="20">
         <f>Assumptions!C9</f>
         <v/>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="20">
         <f>Assumptions!D9</f>
         <v/>
       </c>
@@ -1569,15 +1581,15 @@
           <t>Votes per bout</t>
         </is>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="18">
         <f>B7*B9</f>
         <v/>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="18">
         <f>C7*C9</f>
         <v/>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="18">
         <f>D7*D9</f>
         <v/>
       </c>
@@ -1588,19 +1600,19 @@
           <t>Annual votes</t>
         </is>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="19">
         <f>B6*B10</f>
         <v/>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="19">
         <f>C6*C10</f>
         <v/>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="19">
         <f>D6*D10</f>
         <v/>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="19">
         <f>SUM(B11:D11)</f>
         <v/>
       </c>
@@ -1611,15 +1623,15 @@
           <t>Avg minutes watched / live viewer</t>
         </is>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="18">
         <f>Assumptions!B34</f>
         <v/>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="18">
         <f>Assumptions!C34</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="18">
         <f>Assumptions!D34</f>
         <v/>
       </c>
@@ -1630,33 +1642,33 @@
           <t>Annual viewer-hours delivered (Mux)</t>
         </is>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="19">
         <f>B8*(B13+Assumptions!B35*Assumptions!B36)/60</f>
         <v/>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="19">
         <f>C8*(C13+Assumptions!C35*Assumptions!C36)/60</f>
         <v/>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="19">
         <f>D8*(D13+Assumptions!D35*Assumptions!D36)/60</f>
         <v/>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="19">
         <f>SUM(B14:D14)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>REACH BEYOND LIVE</t>
         </is>
       </c>
-      <c r="B16" s="21" t="n"/>
-      <c r="C16" s="21" t="n"/>
-      <c r="D16" s="21" t="n"/>
-      <c r="E16" s="21" t="n"/>
+      <c r="B16" s="22" t="n"/>
+      <c r="C16" s="22" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="22" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -1664,15 +1676,15 @@
           <t>Post-live replay multiplier</t>
         </is>
       </c>
-      <c r="B17" s="22">
+      <c r="B17" s="23">
         <f>Assumptions!B35</f>
         <v/>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="23">
         <f>Assumptions!C35</f>
         <v/>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="23">
         <f>Assumptions!D35</f>
         <v/>
       </c>
@@ -1683,15 +1695,15 @@
           <t>Replay viewers / bout</t>
         </is>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="18">
         <f>B7*B17</f>
         <v/>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="18">
         <f>C7*C17</f>
         <v/>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="18">
         <f>D7*D17</f>
         <v/>
       </c>
@@ -1702,15 +1714,15 @@
           <t>Total reach / bout (live + replay)</t>
         </is>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="18">
         <f>B7+B18</f>
         <v/>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="18">
         <f>C7+C18</f>
         <v/>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="18">
         <f>D7+D18</f>
         <v/>
       </c>
@@ -1721,19 +1733,19 @@
           <t>Annual total impressions</t>
         </is>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="19">
         <f>B6*B19</f>
         <v/>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="19">
         <f>C6*C19</f>
         <v/>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="19">
         <f>D6*D19</f>
         <v/>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="19">
         <f>SUM(B20:D20)</f>
         <v/>
       </c>
@@ -1775,37 +1787,37 @@
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="5" t="inlineStr"/>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>3-Yr Total</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>REVENUE</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n"/>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="24" t="n"/>
-      <c r="E6" s="24" t="n"/>
+      <c r="B6" s="25" t="n"/>
+      <c r="C6" s="25" t="n"/>
+      <c r="D6" s="25" t="n"/>
+      <c r="E6" s="25" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1813,19 +1825,19 @@
           <t>Voting revenue</t>
         </is>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <f>'Bouts &amp; Audience'!B11*Assumptions!B10</f>
         <v/>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <f>'Bouts &amp; Audience'!C11*Assumptions!C10</f>
         <v/>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <f>'Bouts &amp; Audience'!D11*Assumptions!D10</f>
         <v/>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <f>SUM(B7:D7)</f>
         <v/>
       </c>
@@ -1836,33 +1848,33 @@
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="27">
         <f>B7</f>
         <v/>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="27">
         <f>C7</f>
         <v/>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <f>D7</f>
         <v/>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <f>SUM(B9:D9)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>VARIABLE COSTS  ·  COGS</t>
         </is>
       </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
+      <c r="B11" s="22" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1870,15 +1882,15 @@
           <t>Mux delivery (CDN)</t>
         </is>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="26">
         <f>'Bouts &amp; Audience'!B14*Assumptions!B17</f>
         <v/>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="26">
         <f>'Bouts &amp; Audience'!C14*Assumptions!C17</f>
         <v/>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <f>'Bouts &amp; Audience'!D14*Assumptions!D17</f>
         <v/>
       </c>
@@ -1889,15 +1901,15 @@
           <t>Mux ingest</t>
         </is>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="26">
         <f>Assumptions!B7*Assumptions!B18</f>
         <v/>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <f>Assumptions!C7*Assumptions!C18</f>
         <v/>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <f>Assumptions!D7*Assumptions!D18</f>
         <v/>
       </c>
@@ -1908,15 +1920,15 @@
           <t>Stripe processing</t>
         </is>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="26">
         <f>B7*Assumptions!B19+'Bouts &amp; Audience'!B11*Assumptions!B20</f>
         <v/>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="26">
         <f>C7*Assumptions!C19+'Bouts &amp; Audience'!C11*Assumptions!C20</f>
         <v/>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <f>D7*Assumptions!D19+'Bouts &amp; Audience'!D11*Assumptions!D20</f>
         <v/>
       </c>
@@ -1927,15 +1939,15 @@
           <t>Charity payout (18% of vote rev)</t>
         </is>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="26">
         <f>B7*Assumptions!B21</f>
         <v/>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="26">
         <f>C7*Assumptions!C21</f>
         <v/>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="26">
         <f>D7*Assumptions!D21</f>
         <v/>
       </c>
@@ -1946,15 +1958,15 @@
           <t>Debater honorariums</t>
         </is>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="26">
         <f>Assumptions!B7*Assumptions!B22</f>
         <v/>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <f>Assumptions!C7*Assumptions!C22</f>
         <v/>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <f>Assumptions!D7*Assumptions!D22</f>
         <v/>
       </c>
@@ -1965,15 +1977,15 @@
           <t>Production</t>
         </is>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="26">
         <f>Assumptions!B7*Assumptions!B23</f>
         <v/>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="26">
         <f>Assumptions!C7*Assumptions!C23</f>
         <v/>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="26">
         <f>Assumptions!D7*Assumptions!D23</f>
         <v/>
       </c>
@@ -1984,19 +1996,19 @@
           <t>Total variable cost</t>
         </is>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="27">
         <f>SUM(B12:B17)</f>
         <v/>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="27">
         <f>SUM(C12:C17)</f>
         <v/>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="27">
         <f>SUM(D12:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="27">
         <f>SUM(B18:D18)</f>
         <v/>
       </c>
@@ -2018,19 +2030,19 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="27">
         <f>B9-B18</f>
         <v/>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="27">
         <f>C9-C18</f>
         <v/>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="27">
         <f>D9-D18</f>
         <v/>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="27">
         <f>SUM(B21:D21)</f>
         <v/>
       </c>
@@ -2041,29 +2053,29 @@
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="20">
         <f>IFERROR(B21/B9,0)</f>
         <v/>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="20">
         <f>IFERROR(C21/C9,0)</f>
         <v/>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="20">
         <f>IFERROR(D21/D9,0)</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>FIXED OPEX</t>
         </is>
       </c>
-      <c r="B24" s="21" t="n"/>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="22" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -2071,15 +2083,15 @@
           <t>Headcount cost</t>
         </is>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="26">
         <f>Assumptions!B26*Assumptions!B27</f>
         <v/>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="26">
         <f>Assumptions!C26*Assumptions!C27</f>
         <v/>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="26">
         <f>Assumptions!D26*Assumptions!D27</f>
         <v/>
       </c>
@@ -2090,15 +2102,15 @@
           <t>Paid search &amp; acquisition</t>
         </is>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="26">
         <f>Assumptions!B28</f>
         <v/>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="26">
         <f>Assumptions!C28</f>
         <v/>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="26">
         <f>Assumptions!D28</f>
         <v/>
       </c>
@@ -2109,15 +2121,15 @@
           <t>Brand &amp; creator marketing</t>
         </is>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="26">
         <f>Assumptions!B29</f>
         <v/>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="26">
         <f>Assumptions!C29</f>
         <v/>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="26">
         <f>Assumptions!D29</f>
         <v/>
       </c>
@@ -2128,15 +2140,15 @@
           <t>G&amp;A, tooling, infra</t>
         </is>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="26">
         <f>Assumptions!B30</f>
         <v/>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="26">
         <f>Assumptions!C30</f>
         <v/>
       </c>
-      <c r="D28" s="25">
+      <c r="D28" s="26">
         <f>Assumptions!D30</f>
         <v/>
       </c>
@@ -2147,15 +2159,15 @@
           <t>Legal, accounting, insurance</t>
         </is>
       </c>
-      <c r="B29" s="25">
+      <c r="B29" s="26">
         <f>Assumptions!B31</f>
         <v/>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="26">
         <f>Assumptions!C31</f>
         <v/>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="26">
         <f>Assumptions!D31</f>
         <v/>
       </c>
@@ -2166,19 +2178,19 @@
           <t>Total fixed opex</t>
         </is>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="27">
         <f>SUM(B25:B29)</f>
         <v/>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="27">
         <f>SUM(C25:C29)</f>
         <v/>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="27">
         <f>SUM(D25:D29)</f>
         <v/>
       </c>
-      <c r="E30" s="26">
+      <c r="E30" s="27">
         <f>SUM(B30:D30)</f>
         <v/>
       </c>
@@ -2200,19 +2212,19 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B33" s="26">
+      <c r="B33" s="27">
         <f>B21-B30</f>
         <v/>
       </c>
-      <c r="C33" s="26">
+      <c r="C33" s="27">
         <f>C21-C30</f>
         <v/>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="27">
         <f>D21-D30</f>
         <v/>
       </c>
-      <c r="E33" s="26">
+      <c r="E33" s="27">
         <f>SUM(B33:D33)</f>
         <v/>
       </c>
@@ -2223,15 +2235,15 @@
           <t>EBITDA margin %</t>
         </is>
       </c>
-      <c r="B34" s="19">
+      <c r="B34" s="20">
         <f>IFERROR(B33/B9,0)</f>
         <v/>
       </c>
-      <c r="C34" s="19">
+      <c r="C34" s="20">
         <f>IFERROR(C33/C9,0)</f>
         <v/>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="20">
         <f>IFERROR(D33/D9,0)</f>
         <v/>
       </c>
@@ -2280,17 +2292,17 @@
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="5" t="inlineStr"/>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Year 1 scale</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Year 2 scale</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>Year 3 scale</t>
         </is>
@@ -2302,15 +2314,15 @@
           <t>Avg viewers / bout</t>
         </is>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="18">
         <f>Assumptions!B8</f>
         <v/>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="18">
         <f>Assumptions!C8</f>
         <v/>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="18">
         <f>Assumptions!D8</f>
         <v/>
       </c>
@@ -2321,28 +2333,28 @@
           <t>Voters / bout</t>
         </is>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="18">
         <f>B6*Assumptions!B9</f>
         <v/>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="18">
         <f>C6*Assumptions!C9</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="18">
         <f>D6*Assumptions!D9</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>REVENUE / BOUT</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n"/>
-      <c r="C9" s="24" t="n"/>
-      <c r="D9" s="24" t="n"/>
+      <c r="B9" s="25" t="n"/>
+      <c r="C9" s="25" t="n"/>
+      <c r="D9" s="25" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -2350,15 +2362,15 @@
           <t>Voting</t>
         </is>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="26">
         <f>B7*Assumptions!B10</f>
         <v/>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <f>C7*Assumptions!C10</f>
         <v/>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <f>D7*Assumptions!D10</f>
         <v/>
       </c>
@@ -2369,28 +2381,28 @@
           <t>Total revenue / bout</t>
         </is>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="27">
         <f>B10</f>
         <v/>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <f>C10</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>D10</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>VARIABLE COST / BOUT</t>
         </is>
       </c>
-      <c r="B14" s="21" t="n"/>
-      <c r="C14" s="21" t="n"/>
-      <c r="D14" s="21" t="n"/>
+      <c r="B14" s="22" t="n"/>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="22" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -2398,15 +2410,15 @@
           <t>Mux delivery (live + replay)</t>
         </is>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="26">
         <f>B6*(Assumptions!B34+Assumptions!B35*Assumptions!B36)/60*Assumptions!B17</f>
         <v/>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="26">
         <f>C6*(Assumptions!C34+Assumptions!C35*Assumptions!C36)/60*Assumptions!C17</f>
         <v/>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="26">
         <f>D6*(Assumptions!D34+Assumptions!D35*Assumptions!D36)/60*Assumptions!D17</f>
         <v/>
       </c>
@@ -2417,15 +2429,15 @@
           <t>Mux ingest</t>
         </is>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="26">
         <f>Assumptions!B18</f>
         <v/>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <f>Assumptions!C18</f>
         <v/>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <f>Assumptions!D18</f>
         <v/>
       </c>
@@ -2436,15 +2448,15 @@
           <t>Stripe processing</t>
         </is>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="26">
         <f>B10*Assumptions!B19+B7*Assumptions!B20</f>
         <v/>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="26">
         <f>C10*Assumptions!C19+C7*Assumptions!C20</f>
         <v/>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="26">
         <f>D10*Assumptions!D19+D7*Assumptions!D20</f>
         <v/>
       </c>
@@ -2455,15 +2467,15 @@
           <t>Charity payout</t>
         </is>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="26">
         <f>B10*Assumptions!B21</f>
         <v/>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="26">
         <f>C10*Assumptions!C21</f>
         <v/>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="26">
         <f>D10*Assumptions!D21</f>
         <v/>
       </c>
@@ -2474,15 +2486,15 @@
           <t>Debater honorariums</t>
         </is>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="26">
         <f>Assumptions!B22</f>
         <v/>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="26">
         <f>Assumptions!C22</f>
         <v/>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="26">
         <f>Assumptions!D22</f>
         <v/>
       </c>
@@ -2493,15 +2505,15 @@
           <t>Production</t>
         </is>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="26">
         <f>Assumptions!B23</f>
         <v/>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="26">
         <f>Assumptions!C23</f>
         <v/>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="26">
         <f>Assumptions!D23</f>
         <v/>
       </c>
@@ -2512,15 +2524,15 @@
           <t>Total variable cost / bout</t>
         </is>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="27">
         <f>SUM(B15:B20)</f>
         <v/>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="27">
         <f>SUM(C15:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="27">
         <f>SUM(D15:D20)</f>
         <v/>
       </c>
@@ -2541,15 +2553,15 @@
           <t>Contribution $</t>
         </is>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="27">
         <f>B12-B21</f>
         <v/>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="27">
         <f>C12-C21</f>
         <v/>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="27">
         <f>D12-D21</f>
         <v/>
       </c>
@@ -2560,15 +2572,15 @@
           <t>Contribution %</t>
         </is>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="20">
         <f>IFERROR(B24/B12,0)</f>
         <v/>
       </c>
-      <c r="C25" s="19">
+      <c r="C25" s="20">
         <f>IFERROR(C24/C12,0)</f>
         <v/>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="20">
         <f>IFERROR(D24/D12,0)</f>
         <v/>
       </c>

--- a/Argumental/argumental-app/public/argumental-financial-model.xlsx
+++ b/Argumental/argumental-app/public/argumental-financial-model.xlsx
@@ -20,13 +20,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.000"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;0.00"/>
     <numFmt numFmtId="168" formatCode="#,##0&quot;x&quot;"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0)"/>
+    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0)"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -137,20 +138,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -164,13 +166,13 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="9" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -179,8 +181,8 @@
     <xf numFmtId="168" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -194,18 +196,22 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -573,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A50"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -582,7 +588,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ARGUMENTAL · INVESTOR MODEL · 3-YEAR</t>
+          <t>ARGUMENTAL · INVESTOR MODEL · 3-YEAR · AGGRESSIVE CASE</t>
         </is>
       </c>
     </row>
@@ -599,305 +605,277 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>This workbook is the working financial model behind the Argumental seed deck.</t>
+          <t>This workbook renders the Aggressive scenario, the default case</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Inputs are loaded from src/lib/financialModelInputs.json — the same file that</t>
+          <t>shown on /deck and /model. Inputs come from</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>drives /deck and /model on the website. Edit the JSON, re-run the build</t>
+          <t>src/lib/financialModelInputs.json — the same file that drives the</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>script, and all three views stay in lockstep.</t>
+          <t>TypeScript views.  Edit the JSON, re-run this script, and all three</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>(deck · dashboard · spreadsheet) stay in lockstep.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Tabs</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. Read Me — this page.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Assumptions — every input the model uses, in one place. Cells with a</t>
+          <t xml:space="preserve">  1. Read Me — this page.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     pale-blue fill are inputs; everything else is a formula.</t>
+          <t xml:space="preserve">  2. Assumptions — every input the model uses, in one place.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Bouts &amp; Audience — viewer ramp, replay reach, votes per year.</t>
+          <t xml:space="preserve">     Pale-blue cells = inputs; everything else is a formula.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. P&amp;L (3-Year) — revenue, variable costs, gross margin, fixed opex,</t>
+          <t xml:space="preserve">  3. Bouts &amp; Audience — viewer ramp, replay reach, votes.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     EBITDA. Year-over-year columns plus a running 3-year total.</t>
+          <t xml:space="preserve">  4. P&amp;L (3-Year) — full revenue stack, variable costs, gross margin,</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. Unit Economics — contribution margin per bout at three audience scales.</t>
+          <t xml:space="preserve">     fixed opex, EBITDA, year-over-year + 3-Yr total.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Unit Economics — per-bout contribution margin, three audience scales.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Conventions</t>
-        </is>
-      </c>
+      <c r="A18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · Pale-blue cells = inputs.  All other cells are formulas — don't overwrite.</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 stated goal</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Red headers = revenue.  Blue headers = costs.  Black headers = totals.</t>
+          <t xml:space="preserve">  · 60,000 live viewers per bout by end of Year 1.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · Bouts cadence is one per Sunday — 4 / month, 48 / year.</t>
-        </is>
-      </c>
+      <c r="A21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · All dollar figures are in USD.  Years labeled 2026 / 2027 / 2028.</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Reach assumption — the 41× multiplier</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 41× total impressions per bout (live + post-live replay).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Year 1 stated goal</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 80% of replay viewing happens off-platform on FB / TikTok / YouTube.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · 60,000 live viewers per bout by end of Year 1.</t>
+          <t xml:space="preserve">    Mux delivers only the on-platform portion; off-platform impressions</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    earn ad share from the host platforms.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Reach assumption — the 41× multiplier</t>
-        </is>
-      </c>
+      <c r="A27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · Live + post-live replay = 41× total impressions per bout. Each</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>What the aggressive case has built in</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    archived bout earns ~40× the live-viewer count over its first 24 hours</t>
+          <t xml:space="preserve">  · Voting revenue at $5 / vote, $10 / week cap, gated by live reach.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    via clips, embeds, and on-demand replay. Replay viewers don't vote</t>
+          <t xml:space="preserve">  · Sponsorship — title slots ramping from Y1 to full cadence in Y3.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (the bout is over) but they DO drive Mux delivery cost and sponsor</t>
+          <t xml:space="preserve">  · Premium subscription — $7 / month archive + AMA tier.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    package value.  The model accounts for both.</t>
+          <t xml:space="preserve">  · Live championship ticketing — physical events Y2 and Y3.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr"/>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Merch + international format licensing.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>What this model is honest about</t>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · YouTube ad share at $1.50 CPM on off-platform replay views.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Voting revenue is gated by live viewer reach, not by price.</t>
+          <t xml:space="preserve">  · Off-platform replay distribution (saves Mux delivery cost).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Mux delivery cost scales with viewers (live + replay); included as a</t>
+          <t xml:space="preserve">  · Honoraria: Y1 flat $10K, Y2/Y3 revenue share (5% / 3% of bout purse).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    real per-bout COGS.</t>
+          <t xml:space="preserve">  · Charity payout 18% of voting revenue, accounted as COGS.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Charity payout is 18% of gross voting revenue, accounted as COGS.</t>
+          <t xml:space="preserve">  · Mux enterprise rate by Y3 ($0.025 / viewer-hr).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Debater honorariums: Y1 flat $10K / bout (cash to attract talent),</t>
+          <t xml:space="preserve">  · Lean headcount: 4 → 7 → 10 FTE.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Y2/Y3 revenue share — 5% / 3% of per-bout voting purse — to align</t>
-        </is>
-      </c>
+      <c r="A40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    debater incentives with audience growth as the league matures.</t>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>What this model deliberately omits</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr"/>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Working-capital and payment-processor float.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>What this model deliberately omits</t>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · Tax — model is pre-tax EBITDA only.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · Sponsorship revenue. Title slots, category exclusives, and brand</t>
-        </is>
-      </c>
+      <c r="A44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    integrations are real revenue lines for the league but treated as</t>
+          <t>For the conservative floor case (voting only, full headcount, no</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    upside here — the conservative case is voting revenue only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · IP / licensing revenue (international territories, format licensing).</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · On-demand archive monetization, white-label league, ticketing, merch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · Working-capital and payment-processor float.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · Tax — model is pre-tax EBITDA only.</t>
+          <t>off-platform replay), see /model?scenario=conservative on the website.</t>
         </is>
       </c>
     </row>
@@ -912,7 +890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -925,7 +903,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>INPUTS — EDIT THESE TO STRESS-TEST</t>
+          <t>INPUTS — AGGRESSIVE SCENARIO</t>
         </is>
       </c>
     </row>
@@ -942,22 +920,22 @@
           <t>Driver</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>2026 (Y1)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>2027 (Y2)</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>2028 (Y3)</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -969,92 +947,145 @@
           <t>AUDIENCE &amp; ENGAGEMENT</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Bouts per year</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>1 / Sunday</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Avg concurrent live viewers / bout</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="9" t="n">
         <v>60000</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="9" t="n">
         <v>100000</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="9" t="n">
         <v>125000</v>
       </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Y1 ramp targets 100K EOY</t>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Y1 EOY peak target: 60,000</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>% of viewers who vote</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="11" t="n">
         <v>0.06</v>
       </c>
-      <c r="C9" s="10" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="C9" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Single $5 vote</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Avg vote price (USD)</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Sponsor revenue / bout (USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Title slot · 41× reach</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Sponsored bouts (% of cadence)</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Brand fit</t>
         </is>
       </c>
     </row>
@@ -1064,155 +1095,155 @@
           <t>VARIABLE COSTS  ·  PER BOUT</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Mux delivery $/viewer-hour</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="14" t="n">
         <v>0.06</v>
       </c>
-      <c r="C17" s="12" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D17" s="12" t="n">
+      <c r="C17" s="14" t="n">
         <v>0.05</v>
       </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>Negotiated at scale</t>
+      <c r="D17" s="14" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Y3 = enterprise rate</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Mux ingest $/bout (2 streams)</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B18" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>24m × 2 streams</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Stripe rate (% of vote rev)</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B19" s="11" t="n">
         <v>0.029</v>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C19" s="11" t="n">
         <v>0.029</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="11" t="n">
         <v>0.029</v>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>+ $0.30/vote</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Stripe per-vote fee</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
+      <c r="B20" s="15" t="n">
         <v>0.3</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="15" t="n">
         <v>0.3</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="15" t="n">
         <v>0.3</v>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Flat</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Charity payout (% of vote rev)</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n">
+      <c r="B21" s="13" t="n">
         <v>0.18</v>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="13" t="n">
         <v>0.18</v>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="13" t="n">
         <v>0.18</v>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>18% donor model</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Debater honorarium / bout</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n">
+      <c r="B22" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="16">
         <f>C8*C9*C10*0.05</f>
         <v/>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="16">
         <f>D8*D9*D10*0.03</f>
         <v/>
       </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>Y1 flat $10,000 · Y2 5% of purse · Y3 3% of purse</t>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>Y1 flat $10,000 · Y2 5% · Y3 3% of purse</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Production / bout</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n">
+      <c r="B23" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="C23" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>Studio + crew</t>
         </is>
@@ -1224,132 +1255,132 @@
           <t>FIXED COSTS  ·  PER YEAR</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Headcount (FTE)</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n">
+      <c r="B26" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C26" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>Avg loaded $180K</t>
+      <c r="C26" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Avg loaded ~$185K</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Loaded cost per FTE</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B27" s="12" t="n">
         <v>180000</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>180000</v>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>195000</v>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="C27" s="12" t="n">
+        <v>185000</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>190000</v>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>Salary + benefits</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Paid search &amp; acquisition</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n">
+      <c r="B28" s="12" t="n">
         <v>120000</v>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="C28" s="12" t="n">
         <v>240000</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D28" s="12" t="n">
         <v>360000</v>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>$10K/mo Y1</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Brand &amp; creator marketing</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n">
+      <c r="B29" s="12" t="n">
         <v>60000</v>
       </c>
-      <c r="C29" s="11" t="n">
+      <c r="C29" s="12" t="n">
         <v>240000</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="12" t="n">
         <v>480000</v>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>Sponsored clips</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>G&amp;A, tooling, infra</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" s="12" t="n">
         <v>60000</v>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="C30" s="12" t="n">
         <v>120000</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>Office, software</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Legal, accounting, insurance</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n">
+      <c r="B31" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="C31" s="12" t="n">
         <v>90000</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="12" t="n">
         <v>140000</v>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>Outside counsel</t>
         </is>
@@ -1361,71 +1392,261 @@
           <t>AUDIENCE BEHAVIOR</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>Avg minutes watched / live viewer</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n">
+      <c r="B34" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="C34" s="8" t="n">
+      <c r="C34" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="D34" s="8" t="n">
+      <c r="D34" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>Drives live Mux delivery cost</t>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Drives Mux live-delivery cost</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>Post-live replay multiplier</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
+      <c r="B35" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="C35" s="16" t="n">
+      <c r="C35" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="D35" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>Replay views = live × this</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>Avg minutes watched / replay viewer</t>
         </is>
       </c>
-      <c r="B36" s="8" t="n">
+      <c r="B36" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C36" s="8" t="n">
+      <c r="C36" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>Highlights &amp; clips</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>PLATFORM REVENUE &amp; DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Premium subscribers (year-end)</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>Archive + AMAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Premium price / mo</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>Flat across years</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Live championship events / yr</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Physical venue</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Seats per event</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Avg ticket price</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Merch annual revenue</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>Belts, jerseys, books</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>International licensing</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>250000</v>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>Format · territories</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Off-platform replay %</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C46" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D46" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>FB · TikTok · YouTube share of replay</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Ad-share CPM (off-platform)</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C47" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D47" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>YouTube AdSense estimate</t>
         </is>
       </c>
     </row>
@@ -1470,282 +1691,282 @@
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>3-Yr Total</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Bouts per year</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <f>Assumptions!B7</f>
         <v/>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <f>Assumptions!C7</f>
         <v/>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="19">
         <f>Assumptions!D7</f>
         <v/>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <f>SUM(B6:D6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Avg concurrent viewers / bout</t>
-        </is>
-      </c>
-      <c r="B7" s="18">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Avg concurrent live viewers / bout</t>
+        </is>
+      </c>
+      <c r="B7" s="19">
         <f>Assumptions!B8</f>
         <v/>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <f>Assumptions!C8</f>
         <v/>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="19">
         <f>Assumptions!D8</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Annual viewer-bouts</t>
-        </is>
-      </c>
-      <c r="B8" s="18">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Annual viewer-bouts (live)</t>
+        </is>
+      </c>
+      <c r="B8" s="19">
         <f>B6*B7</f>
         <v/>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <f>C6*C7</f>
         <v/>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="19">
         <f>D6*D7</f>
         <v/>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <f>SUM(B8:D8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Voter conversion rate</t>
         </is>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="21">
         <f>Assumptions!B9</f>
         <v/>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="21">
         <f>Assumptions!C9</f>
         <v/>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="21">
         <f>Assumptions!D9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Votes per bout</t>
         </is>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <f>B7*B9</f>
         <v/>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="19">
         <f>C7*C9</f>
         <v/>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="19">
         <f>D7*D9</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Annual votes</t>
         </is>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="20">
         <f>B6*B10</f>
         <v/>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="20">
         <f>C6*C10</f>
         <v/>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="20">
         <f>D6*D10</f>
         <v/>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="20">
         <f>SUM(B11:D11)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Avg minutes watched / live viewer</t>
         </is>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="19">
         <f>Assumptions!B34</f>
         <v/>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="19">
         <f>Assumptions!C34</f>
         <v/>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="19">
         <f>Assumptions!D34</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Annual viewer-hours delivered (Mux)</t>
         </is>
       </c>
-      <c r="B14" s="19">
-        <f>B8*(B13+Assumptions!B35*Assumptions!B36)/60</f>
-        <v/>
-      </c>
-      <c r="C14" s="19">
-        <f>C8*(C13+Assumptions!C35*Assumptions!C36)/60</f>
-        <v/>
-      </c>
-      <c r="D14" s="19">
-        <f>D8*(D13+Assumptions!D35*Assumptions!D36)/60</f>
-        <v/>
-      </c>
-      <c r="E14" s="19">
+      <c r="B14" s="20">
+        <f>B6*(B7*B13+B7*Assumptions!B35*Assumptions!B36*(1-Assumptions!B46))/60</f>
+        <v/>
+      </c>
+      <c r="C14" s="20">
+        <f>C6*(C7*C13+C7*Assumptions!C35*Assumptions!C36*(1-Assumptions!C46))/60</f>
+        <v/>
+      </c>
+      <c r="D14" s="20">
+        <f>D6*(D7*D13+D7*Assumptions!D35*Assumptions!D36*(1-Assumptions!D46))/60</f>
+        <v/>
+      </c>
+      <c r="E14" s="20">
         <f>SUM(B14:D14)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>REACH BEYOND LIVE</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="22" t="n"/>
-      <c r="E16" s="22" t="n"/>
+      <c r="B16" s="23" t="n"/>
+      <c r="C16" s="23" t="n"/>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="23" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Post-live replay multiplier</t>
         </is>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="24">
         <f>Assumptions!B35</f>
         <v/>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="24">
         <f>Assumptions!C35</f>
         <v/>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="24">
         <f>Assumptions!D35</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Replay viewers / bout</t>
         </is>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="19">
         <f>B7*B17</f>
         <v/>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="19">
         <f>C7*C17</f>
         <v/>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="19">
         <f>D7*D17</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Total reach / bout (live + replay)</t>
         </is>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="19">
         <f>B7+B18</f>
         <v/>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="19">
         <f>C7+C18</f>
         <v/>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="19">
         <f>D7+D18</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Annual total impressions</t>
         </is>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="20">
         <f>B6*B19</f>
         <v/>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="20">
         <f>C6*C19</f>
         <v/>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="20">
         <f>D6*D19</f>
         <v/>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="20">
         <f>SUM(B20:D20)</f>
         <v/>
       </c>
@@ -1761,7 +1982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1995,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>REVENUE  ·  VARIABLE COSTS  ·  GROSS MARGIN  ·  OPEX  ·  EBITDA</t>
+          <t>FULL P&amp;L  ·  REVENUE  ·  COGS  ·  GROSS MARGIN  ·  OPEX  ·  EBITDA</t>
         </is>
       </c>
     </row>
@@ -1787,77 +2008,100 @@
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="5" t="inlineStr"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>3-Yr Total</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>REVENUE</t>
         </is>
       </c>
-      <c r="B6" s="25" t="n"/>
-      <c r="C6" s="25" t="n"/>
-      <c r="D6" s="25" t="n"/>
-      <c r="E6" s="25" t="n"/>
+      <c r="B6" s="26" t="n"/>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="26" t="n"/>
+      <c r="E6" s="26" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Voting revenue</t>
         </is>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <f>'Bouts &amp; Audience'!B11*Assumptions!B10</f>
         <v/>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <f>'Bouts &amp; Audience'!C11*Assumptions!C10</f>
         <v/>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>'Bouts &amp; Audience'!D11*Assumptions!D10</f>
         <v/>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>SUM(B7:D7)</f>
         <v/>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Sponsor revenue</t>
+        </is>
+      </c>
+      <c r="B8" s="27">
+        <f>Assumptions!B7*Assumptions!B14*Assumptions!B13</f>
+        <v/>
+      </c>
+      <c r="C8" s="27">
+        <f>Assumptions!C7*Assumptions!C14*Assumptions!C13</f>
+        <v/>
+      </c>
+      <c r="D8" s="27">
+        <f>Assumptions!D7*Assumptions!D14*Assumptions!D13</f>
+        <v/>
+      </c>
+      <c r="E8" s="27">
+        <f>SUM(B8:D8)</f>
+        <v/>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Total revenue</t>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Premium subscriptions</t>
         </is>
       </c>
       <c r="B9" s="27">
-        <f>B7</f>
+        <f>Assumptions!B39*Assumptions!B40*12</f>
         <v/>
       </c>
       <c r="C9" s="27">
-        <f>C7</f>
+        <f>Assumptions!C39*Assumptions!C40*12</f>
         <v/>
       </c>
       <c r="D9" s="27">
-        <f>D7</f>
+        <f>Assumptions!D39*Assumptions!D40*12</f>
         <v/>
       </c>
       <c r="E9" s="27">
@@ -1865,393 +2109,508 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="21" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Live championship ticketing</t>
+        </is>
+      </c>
+      <c r="B10" s="27">
+        <f>Assumptions!B41*Assumptions!B42*Assumptions!B43</f>
+        <v/>
+      </c>
+      <c r="C10" s="27">
+        <f>Assumptions!C41*Assumptions!C42*Assumptions!C43</f>
+        <v/>
+      </c>
+      <c r="D10" s="27">
+        <f>Assumptions!D41*Assumptions!D42*Assumptions!D43</f>
+        <v/>
+      </c>
+      <c r="E10" s="27">
+        <f>SUM(B10:D10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Merch</t>
+        </is>
+      </c>
+      <c r="B11" s="27">
+        <f>Assumptions!B44</f>
+        <v/>
+      </c>
+      <c r="C11" s="27">
+        <f>Assumptions!C44</f>
+        <v/>
+      </c>
+      <c r="D11" s="27">
+        <f>Assumptions!D44</f>
+        <v/>
+      </c>
+      <c r="E11" s="27">
+        <f>SUM(B11:D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>International licensing</t>
+        </is>
+      </c>
+      <c r="B12" s="27">
+        <f>Assumptions!B45</f>
+        <v/>
+      </c>
+      <c r="C12" s="27">
+        <f>Assumptions!C45</f>
+        <v/>
+      </c>
+      <c r="D12" s="27">
+        <f>Assumptions!D45</f>
+        <v/>
+      </c>
+      <c r="E12" s="27">
+        <f>SUM(B12:D12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>YouTube ad share</t>
+        </is>
+      </c>
+      <c r="B13" s="27">
+        <f>Assumptions!B7*Assumptions!B8*Assumptions!B35*Assumptions!B46*Assumptions!B47/1000</f>
+        <v/>
+      </c>
+      <c r="C13" s="27">
+        <f>Assumptions!C7*Assumptions!C8*Assumptions!C35*Assumptions!C46*Assumptions!C47/1000</f>
+        <v/>
+      </c>
+      <c r="D13" s="27">
+        <f>Assumptions!D7*Assumptions!D8*Assumptions!D35*Assumptions!D46*Assumptions!D47/1000</f>
+        <v/>
+      </c>
+      <c r="E13" s="27">
+        <f>SUM(B13:D13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Total revenue</t>
+        </is>
+      </c>
+      <c r="B14" s="28">
+        <f>SUM(B7:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="28">
+        <f>SUM(C7:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="28">
+        <f>SUM(D7:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="28">
+        <f>SUM(B14:D14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>VARIABLE COSTS  ·  COGS</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="22" t="n"/>
-      <c r="E11" s="22" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Mux delivery (CDN)</t>
-        </is>
-      </c>
-      <c r="B12" s="26">
+      <c r="B16" s="23" t="n"/>
+      <c r="C16" s="23" t="n"/>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="23" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Mux delivery (live + on-platform replay)</t>
+        </is>
+      </c>
+      <c r="B17" s="27">
         <f>'Bouts &amp; Audience'!B14*Assumptions!B17</f>
         <v/>
       </c>
-      <c r="C12" s="26">
+      <c r="C17" s="27">
         <f>'Bouts &amp; Audience'!C14*Assumptions!C17</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D17" s="27">
         <f>'Bouts &amp; Audience'!D14*Assumptions!D17</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Mux ingest</t>
         </is>
       </c>
-      <c r="B13" s="26">
+      <c r="B18" s="27">
         <f>Assumptions!B7*Assumptions!B18</f>
         <v/>
       </c>
-      <c r="C13" s="26">
+      <c r="C18" s="27">
         <f>Assumptions!C7*Assumptions!C18</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D18" s="27">
         <f>Assumptions!D7*Assumptions!D18</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Stripe processing</t>
         </is>
       </c>
-      <c r="B14" s="26">
+      <c r="B19" s="27">
         <f>B7*Assumptions!B19+'Bouts &amp; Audience'!B11*Assumptions!B20</f>
         <v/>
       </c>
-      <c r="C14" s="26">
+      <c r="C19" s="27">
         <f>C7*Assumptions!C19+'Bouts &amp; Audience'!C11*Assumptions!C20</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D19" s="27">
         <f>D7*Assumptions!D19+'Bouts &amp; Audience'!D11*Assumptions!D20</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Charity payout (18% of vote rev)</t>
         </is>
       </c>
-      <c r="B15" s="26">
+      <c r="B20" s="27">
         <f>B7*Assumptions!B21</f>
         <v/>
       </c>
-      <c r="C15" s="26">
+      <c r="C20" s="27">
         <f>C7*Assumptions!C21</f>
         <v/>
       </c>
-      <c r="D15" s="26">
+      <c r="D20" s="27">
         <f>D7*Assumptions!D21</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Debater honorariums</t>
         </is>
       </c>
-      <c r="B16" s="26">
+      <c r="B21" s="27">
         <f>Assumptions!B7*Assumptions!B22</f>
         <v/>
       </c>
-      <c r="C16" s="26">
+      <c r="C21" s="27">
         <f>Assumptions!C7*Assumptions!C22</f>
         <v/>
       </c>
-      <c r="D16" s="26">
+      <c r="D21" s="27">
         <f>Assumptions!D7*Assumptions!D22</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Production</t>
         </is>
       </c>
-      <c r="B17" s="26">
+      <c r="B22" s="27">
         <f>Assumptions!B7*Assumptions!B23</f>
         <v/>
       </c>
-      <c r="C17" s="26">
+      <c r="C22" s="27">
         <f>Assumptions!C7*Assumptions!C23</f>
         <v/>
       </c>
-      <c r="D17" s="26">
+      <c r="D22" s="27">
         <f>Assumptions!D7*Assumptions!D23</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Total variable cost</t>
         </is>
       </c>
-      <c r="B18" s="27">
-        <f>SUM(B12:B17)</f>
-        <v/>
-      </c>
-      <c r="C18" s="27">
-        <f>SUM(C12:C17)</f>
-        <v/>
-      </c>
-      <c r="D18" s="27">
-        <f>SUM(D12:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="27">
-        <f>SUM(B18:D18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="B23" s="28">
+        <f>SUM(B17:B22)</f>
+        <v/>
+      </c>
+      <c r="C23" s="28">
+        <f>SUM(C17:C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="28">
+        <f>SUM(D17:D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="28">
+        <f>SUM(B23:D23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>GROSS MARGIN</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B21" s="27">
-        <f>B9-B18</f>
-        <v/>
-      </c>
-      <c r="C21" s="27">
-        <f>C9-C18</f>
-        <v/>
-      </c>
-      <c r="D21" s="27">
-        <f>D9-D18</f>
-        <v/>
-      </c>
-      <c r="E21" s="27">
-        <f>SUM(B21:D21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="B26" s="28">
+        <f>B14-B23</f>
+        <v/>
+      </c>
+      <c r="C26" s="28">
+        <f>C14-C23</f>
+        <v/>
+      </c>
+      <c r="D26" s="28">
+        <f>D14-D23</f>
+        <v/>
+      </c>
+      <c r="E26" s="28">
+        <f>SUM(B26:D26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B22" s="20">
-        <f>IFERROR(B21/B9,0)</f>
-        <v/>
-      </c>
-      <c r="C22" s="20">
-        <f>IFERROR(C21/C9,0)</f>
-        <v/>
-      </c>
-      <c r="D22" s="20">
-        <f>IFERROR(D21/D9,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="B27" s="21">
+        <f>IFERROR(B26/B14,0)</f>
+        <v/>
+      </c>
+      <c r="C27" s="21">
+        <f>IFERROR(C26/C14,0)</f>
+        <v/>
+      </c>
+      <c r="D27" s="21">
+        <f>IFERROR(D26/D14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>FIXED OPEX</t>
         </is>
       </c>
-      <c r="B24" s="22" t="n"/>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="22" t="n"/>
-      <c r="E24" s="22" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Headcount cost</t>
         </is>
       </c>
-      <c r="B25" s="26">
+      <c r="B30" s="27">
         <f>Assumptions!B26*Assumptions!B27</f>
         <v/>
       </c>
-      <c r="C25" s="26">
+      <c r="C30" s="27">
         <f>Assumptions!C26*Assumptions!C27</f>
         <v/>
       </c>
-      <c r="D25" s="26">
+      <c r="D30" s="27">
         <f>Assumptions!D26*Assumptions!D27</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Paid search &amp; acquisition</t>
         </is>
       </c>
-      <c r="B26" s="26">
+      <c r="B31" s="27">
         <f>Assumptions!B28</f>
         <v/>
       </c>
-      <c r="C26" s="26">
+      <c r="C31" s="27">
         <f>Assumptions!C28</f>
         <v/>
       </c>
-      <c r="D26" s="26">
+      <c r="D31" s="27">
         <f>Assumptions!D28</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>Brand &amp; creator marketing</t>
         </is>
       </c>
-      <c r="B27" s="26">
+      <c r="B32" s="27">
         <f>Assumptions!B29</f>
         <v/>
       </c>
-      <c r="C27" s="26">
+      <c r="C32" s="27">
         <f>Assumptions!C29</f>
         <v/>
       </c>
-      <c r="D27" s="26">
+      <c r="D32" s="27">
         <f>Assumptions!D29</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>G&amp;A, tooling, infra</t>
         </is>
       </c>
-      <c r="B28" s="26">
+      <c r="B33" s="27">
         <f>Assumptions!B30</f>
         <v/>
       </c>
-      <c r="C28" s="26">
+      <c r="C33" s="27">
         <f>Assumptions!C30</f>
         <v/>
       </c>
-      <c r="D28" s="26">
+      <c r="D33" s="27">
         <f>Assumptions!D30</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>Legal, accounting, insurance</t>
         </is>
       </c>
-      <c r="B29" s="26">
+      <c r="B34" s="27">
         <f>Assumptions!B31</f>
         <v/>
       </c>
-      <c r="C29" s="26">
+      <c r="C34" s="27">
         <f>Assumptions!C31</f>
         <v/>
       </c>
-      <c r="D29" s="26">
+      <c r="D34" s="27">
         <f>Assumptions!D31</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>Total fixed opex</t>
         </is>
       </c>
-      <c r="B30" s="27">
-        <f>SUM(B25:B29)</f>
-        <v/>
-      </c>
-      <c r="C30" s="27">
-        <f>SUM(C25:C29)</f>
-        <v/>
-      </c>
-      <c r="D30" s="27">
-        <f>SUM(D25:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="27">
-        <f>SUM(B30:D30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="B35" s="28">
+        <f>SUM(B30:B34)</f>
+        <v/>
+      </c>
+      <c r="C35" s="28">
+        <f>SUM(C30:C34)</f>
+        <v/>
+      </c>
+      <c r="D35" s="28">
+        <f>SUM(D30:D34)</f>
+        <v/>
+      </c>
+      <c r="E35" s="28">
+        <f>SUM(B35:D35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B33" s="27">
-        <f>B21-B30</f>
-        <v/>
-      </c>
-      <c r="C33" s="27">
-        <f>C21-C30</f>
-        <v/>
-      </c>
-      <c r="D33" s="27">
-        <f>D21-D30</f>
-        <v/>
-      </c>
-      <c r="E33" s="27">
-        <f>SUM(B33:D33)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="B38" s="28">
+        <f>B26-B35</f>
+        <v/>
+      </c>
+      <c r="C38" s="28">
+        <f>C26-C35</f>
+        <v/>
+      </c>
+      <c r="D38" s="28">
+        <f>D26-D35</f>
+        <v/>
+      </c>
+      <c r="E38" s="28">
+        <f>SUM(B38:D38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>EBITDA margin %</t>
         </is>
       </c>
-      <c r="B34" s="20">
-        <f>IFERROR(B33/B9,0)</f>
-        <v/>
-      </c>
-      <c r="C34" s="20">
-        <f>IFERROR(C33/C9,0)</f>
-        <v/>
-      </c>
-      <c r="D34" s="20">
-        <f>IFERROR(D33/D9,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>Pre-tax. Excludes IP/licensing upside.</t>
+      <c r="B39" s="21">
+        <f>IFERROR(B38/B14,0)</f>
+        <v/>
+      </c>
+      <c r="C39" s="21">
+        <f>IFERROR(C38/C14,0)</f>
+        <v/>
+      </c>
+      <c r="D39" s="21">
+        <f>IFERROR(D38/D14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>Pre-tax. Excludes working-capital float and tax.</t>
         </is>
       </c>
     </row>
@@ -2266,14 +2625,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2292,303 +2650,341 @@
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="5" t="inlineStr"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Year 1 scale</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Year 2 scale</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Year 3 scale</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Avg viewers / bout</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <f>Assumptions!B8</f>
         <v/>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <f>Assumptions!C8</f>
         <v/>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="19">
         <f>Assumptions!D8</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Voters / bout</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <f>B6*Assumptions!B9</f>
         <v/>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <f>C6*Assumptions!C9</f>
         <v/>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="19">
         <f>D6*Assumptions!D9</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>REVENUE / BOUT</t>
         </is>
       </c>
-      <c r="B9" s="25" t="n"/>
-      <c r="C9" s="25" t="n"/>
-      <c r="D9" s="25" t="n"/>
+      <c r="B9" s="26" t="n"/>
+      <c r="C9" s="26" t="n"/>
+      <c r="D9" s="26" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Voting</t>
-        </is>
-      </c>
-      <c r="B10" s="26">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Voting / bout</t>
+        </is>
+      </c>
+      <c r="B10" s="27">
         <f>B7*Assumptions!B10</f>
         <v/>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <f>C7*Assumptions!C10</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <f>D7*Assumptions!D10</f>
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Sponsor / bout (allocated)</t>
+        </is>
+      </c>
+      <c r="B11" s="27">
+        <f>Assumptions!B13*Assumptions!B14</f>
+        <v/>
+      </c>
+      <c r="C11" s="27">
+        <f>Assumptions!C13*Assumptions!C14</f>
+        <v/>
+      </c>
+      <c r="D11" s="27">
+        <f>Assumptions!D13*Assumptions!D14</f>
+        <v/>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Ad share / bout</t>
+        </is>
+      </c>
+      <c r="B12" s="27">
+        <f>Assumptions!B8*Assumptions!B35*Assumptions!B46*Assumptions!B47/1000</f>
+        <v/>
+      </c>
+      <c r="C12" s="27">
+        <f>Assumptions!C8*Assumptions!C35*Assumptions!C46*Assumptions!C47/1000</f>
+        <v/>
+      </c>
+      <c r="D12" s="27">
+        <f>Assumptions!D8*Assumptions!D35*Assumptions!D46*Assumptions!D47/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Total revenue / bout</t>
         </is>
       </c>
-      <c r="B12" s="27">
-        <f>B10</f>
-        <v/>
-      </c>
-      <c r="C12" s="27">
-        <f>C10</f>
-        <v/>
-      </c>
-      <c r="D12" s="27">
-        <f>D10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="B13" s="28">
+        <f>SUM(B10:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="28">
+        <f>SUM(C10:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="28">
+        <f>SUM(D10:D12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>VARIABLE COST / BOUT</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Mux delivery (live + replay)</t>
-        </is>
-      </c>
-      <c r="B15" s="26">
-        <f>B6*(Assumptions!B34+Assumptions!B35*Assumptions!B36)/60*Assumptions!B17</f>
-        <v/>
-      </c>
-      <c r="C15" s="26">
-        <f>C6*(Assumptions!C34+Assumptions!C35*Assumptions!C36)/60*Assumptions!C17</f>
-        <v/>
-      </c>
-      <c r="D15" s="26">
-        <f>D6*(Assumptions!D34+Assumptions!D35*Assumptions!D36)/60*Assumptions!D17</f>
-        <v/>
-      </c>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="23" t="n"/>
+      <c r="D15" s="23" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Mux delivery (live + on-platform replay)</t>
+        </is>
+      </c>
+      <c r="B16" s="27">
+        <f>B6*(Assumptions!B34+Assumptions!B35*Assumptions!B36*(1-Assumptions!B46))/60*Assumptions!B17</f>
+        <v/>
+      </c>
+      <c r="C16" s="27">
+        <f>C6*(Assumptions!C34+Assumptions!C35*Assumptions!C36*(1-Assumptions!C46))/60*Assumptions!C17</f>
+        <v/>
+      </c>
+      <c r="D16" s="27">
+        <f>D6*(Assumptions!D34+Assumptions!D35*Assumptions!D36*(1-Assumptions!D46))/60*Assumptions!D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Mux ingest</t>
         </is>
       </c>
-      <c r="B16" s="26">
+      <c r="B17" s="27">
         <f>Assumptions!B18</f>
         <v/>
       </c>
-      <c r="C16" s="26">
+      <c r="C17" s="27">
         <f>Assumptions!C18</f>
         <v/>
       </c>
-      <c r="D16" s="26">
+      <c r="D17" s="27">
         <f>Assumptions!D18</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Stripe processing</t>
         </is>
       </c>
-      <c r="B17" s="26">
+      <c r="B18" s="27">
         <f>B10*Assumptions!B19+B7*Assumptions!B20</f>
         <v/>
       </c>
-      <c r="C17" s="26">
+      <c r="C18" s="27">
         <f>C10*Assumptions!C19+C7*Assumptions!C20</f>
         <v/>
       </c>
-      <c r="D17" s="26">
+      <c r="D18" s="27">
         <f>D10*Assumptions!D19+D7*Assumptions!D20</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Charity payout</t>
         </is>
       </c>
-      <c r="B18" s="26">
+      <c r="B19" s="27">
         <f>B10*Assumptions!B21</f>
         <v/>
       </c>
-      <c r="C18" s="26">
+      <c r="C19" s="27">
         <f>C10*Assumptions!C21</f>
         <v/>
       </c>
-      <c r="D18" s="26">
+      <c r="D19" s="27">
         <f>D10*Assumptions!D21</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Debater honorariums</t>
         </is>
       </c>
-      <c r="B19" s="26">
+      <c r="B20" s="27">
         <f>Assumptions!B22</f>
         <v/>
       </c>
-      <c r="C19" s="26">
+      <c r="C20" s="27">
         <f>Assumptions!C22</f>
         <v/>
       </c>
-      <c r="D19" s="26">
+      <c r="D20" s="27">
         <f>Assumptions!D22</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Production</t>
         </is>
       </c>
-      <c r="B20" s="26">
+      <c r="B21" s="27">
         <f>Assumptions!B23</f>
         <v/>
       </c>
-      <c r="C20" s="26">
+      <c r="C21" s="27">
         <f>Assumptions!C23</f>
         <v/>
       </c>
-      <c r="D20" s="26">
+      <c r="D21" s="27">
         <f>Assumptions!D23</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Total variable cost / bout</t>
         </is>
       </c>
-      <c r="B21" s="27">
-        <f>SUM(B15:B20)</f>
-        <v/>
-      </c>
-      <c r="C21" s="27">
-        <f>SUM(C15:C20)</f>
-        <v/>
-      </c>
-      <c r="D21" s="27">
-        <f>SUM(D15:D20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="B22" s="28">
+        <f>SUM(B16:B21)</f>
+        <v/>
+      </c>
+      <c r="C22" s="28">
+        <f>SUM(C16:C21)</f>
+        <v/>
+      </c>
+      <c r="D22" s="28">
+        <f>SUM(D16:D21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>CONTRIBUTION MARGIN / BOUT</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Contribution $</t>
         </is>
       </c>
-      <c r="B24" s="27">
-        <f>B12-B21</f>
-        <v/>
-      </c>
-      <c r="C24" s="27">
-        <f>C12-C21</f>
-        <v/>
-      </c>
-      <c r="D24" s="27">
-        <f>D12-D21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="B25" s="28">
+        <f>B13-B22</f>
+        <v/>
+      </c>
+      <c r="C25" s="28">
+        <f>C13-C22</f>
+        <v/>
+      </c>
+      <c r="D25" s="28">
+        <f>D13-D22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Contribution %</t>
         </is>
       </c>
-      <c r="B25" s="20">
-        <f>IFERROR(B24/B12,0)</f>
-        <v/>
-      </c>
-      <c r="C25" s="20">
-        <f>IFERROR(C24/C12,0)</f>
-        <v/>
-      </c>
-      <c r="D25" s="20">
-        <f>IFERROR(D24/D12,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>Excludes fixed opex. See P&amp;L tab for full picture.</t>
+      <c r="B26" s="21">
+        <f>IFERROR(B25/B13,0)</f>
+        <v/>
+      </c>
+      <c r="C26" s="21">
+        <f>IFERROR(C25/C13,0)</f>
+        <v/>
+      </c>
+      <c r="D26" s="21">
+        <f>IFERROR(D25/D13,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Excludes one-off revenue lines (premium subs, ticketing, merch, licensing) and fixed opex.</t>
         </is>
       </c>
     </row>

--- a/Argumental/argumental-app/public/argumental-financial-model.xlsx
+++ b/Argumental/argumental-app/public/argumental-financial-model.xlsx
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>120000</v>
+        <v>48000</v>
       </c>
       <c r="C28" s="12" t="n">
         <v>240000</v>
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>60000</v>
+        <v>20000</v>
       </c>
       <c r="C29" s="12" t="n">
         <v>240000</v>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="C30" s="12" t="n">
         <v>120000</v>
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="C31" s="12" t="n">
         <v>90000</v>

--- a/Argumental/argumental-app/public/argumental-financial-model.xlsx
+++ b/Argumental/argumental-app/public/argumental-financial-model.xlsx
@@ -1215,16 +1215,16 @@
         <v>10000</v>
       </c>
       <c r="C22" s="16">
-        <f>C8*C9*C10*0.05</f>
+        <f>C8*C9*C10*0.1</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>D8*D9*D10*0.03</f>
+        <f>D8*D9*D10*0.1</f>
         <v/>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>Y1 flat $10,000 · Y2 5% · Y3 3% of purse</t>
+          <t>Y1 flat $10,000 · Y2 10% · Y3 10% of purse</t>
         </is>
       </c>
     </row>
